--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.7.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.7.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.7.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.7.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y61"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.7.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L483: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L483: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜7</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]-</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]-</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L60: isolated marker/symbol line :: A</t>
@@ -626,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: '-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]-</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -636,7 +640,7 @@
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L266: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods | suspicious token(s): ticulari9 (letter/digit mix), SEESaeoeetet (odd internal casing) :: p^lygamistic proclivities. â€¢esn The - a*ticulari9 Mousse E...SEESaeoeetet</t>
+          <t>L266: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | suspicious token(s): ticulari9 (letter/digit mix), SEESaeoeetet (odd internal casing) :: p^lygamistic proclivities. •esn The - a*ticulari9 Mousse E...SEESaeoeetet</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>625</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -695,17 +699,13 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>L266: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods | suspicious token(s): ticulari9 (letter/digit mix), SEESaeoeetet (odd internal casing) :: p^lygamistic proclivities. â€¢esn The - a*ticulari9 Mousse E...SEESaeoeetet</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L507: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Rice â€” who have been preying upon the</t>
-        </is>
-      </c>
+          <t>L266: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | suspicious token(s): ticulari9 (letter/digit mix), SEESaeoeetet (odd internal casing) :: p^lygamistic proclivities. •esn The - a*ticulari9 Mousse E...SEESaeoeetet</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A Big Farmersâ€™ Picnic and Speeches by</t>
+          <t>L266: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods | suspicious token(s): ticulari9 (letter/digit mix), SEESaeoeetet (odd internal casing) :: p^lygamistic proclivities. •esn The - a*ticulari9 Mousse E...SEESaeoeetet</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 1</t>
+          <t>L5: isolated marker/symbol line :: ‘7</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -727,13 +727,13 @@
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L267: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -------------------m ---------â€” ever, can be detected by the dateof the nearer than Gibbonsâ€™ which heing a black satchel and sitting on a road.</t>
+          <t>L267: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -------------------m ---------— ever, can be detected by the dateof the nearer than Gibbons’ which heing a black satchel and sitting on a road.</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L267: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -------------------m ---------â€” ever, can be detected by the dateof the nearer than Gibbonsâ€™ which heing a black satchel and sitting on a road.</t>
+          <t>L267: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -------------------m ---------— ever, can be detected by the dateof the nearer than Gibbons’ which heing a black satchel and sitting on a road.</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -789,14 +789,10 @@
           <t>L297: punctuation artifact: double/multiple hyphen | suspicious token(s): werelargecongregations (very long joined token), hisdestinationinsafetyin (very long joined token) :: werelargecongregations both morningand A Form- ----- Chainand Bunta hasthere may besome starting de- | holmreached hisdestinationinsafetyin</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L609: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: his confi confinement.â€”Toronto World.</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Norwich, Conn., July 6.â€”At the conclu-</t>
+          <t>L677: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: has been summoned by telegraph to Mani |-+ — — ------• ------— a nosriogole owned by James</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -808,7 +804,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L292: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: _----------</t>
+          <t>L65: isolated marker/symbol line :: '-</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -824,13 +820,13 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): under12 (letter/digit mix) :: __________________--Magistrate for disregarding the city by-law Boysâ€™ race, under12 yearsof age Distance 75</t>
+          <t>L665: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): under12 (letter/digit mix) :: __________________--Magistrate for disregarding the city by-law Boys’ race, under12 yearsof age Distance 75</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr">
         <is>
-          <t>L639: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | missing space around punctuation :: on the seat,and a lady sitting opposite be- ________________, â€”</t>
+          <t>L639: missing space around punctuation :: on the seat,and a lady sitting opposite be- ________________, —</t>
         </is>
       </c>
       <c r="V4" s="1" t="inlineStr">
@@ -840,7 +836,7 @@
       </c>
       <c r="W4" s="1" t="inlineStr">
         <is>
-          <t>L361: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: SYRACUSE, N.Y., July 5.â€”In the bicycle</t>
+          <t>L361: abbreviation/spacing may be garbled :: SYRACUSE, N.Y., July 5.—In the bicycle</t>
         </is>
       </c>
       <c r="X4" s="1" t="inlineStr"/>
@@ -854,12 +850,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -877,17 +873,13 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>L298: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): ThePeel (odd internal casing) :: â€œThe examination for teachers' certifi- At the Police Court this morning James velopmentetar conduct at thetime ofthe carried were found two revolvers. ThePeel</t>
-        </is>
-      </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L710: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SoUTHAMPToN (odd internal casing) :: SoUTHAMPToN, July 5.â€” A most disastrous</t>
-        </is>
-      </c>
+          <t>L298: suspicious token(s): ThePeel (odd internal casing) :: “The examination for teachers' certifi- At the Police Court this morning James velopmentetar conduct at thetime ofthe carried were found two revolvers. ThePeel</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: lessons from its management. The experi- First-class yachtsâ€”White Wings, of</t>
+          <t>L756: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Catharines Journal.•</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -897,7 +889,11 @@
           <t>L166: isolated marker/symbol line :: A</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L80: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr">
         <is>
           <t>L450: punctuation artifact: repeated periods | abbreviation/spacing may be garbled :: Mr. J.D. Bissonnette, B.A., is in charge...</t>
@@ -956,19 +952,11 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>L306: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN, U+00A4 CURRENCY SIGN | suspicious token(s): neWelaeCANT (odd internal casing) :: 0-3 - -aà¥¤^^^neWelaeCANT</t>
-        </is>
-      </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”While Mr. A Marshall, of Middleport,</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Second-class yachtsâ€”Caprice, Toronto,</t>
-        </is>
-      </c>
+          <t>L306: suspicious token(s): neWelaeCANT (odd internal casing) :: 0-3 - -a।^^^neWelaeCANT</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -976,7 +964,11 @@
           <t>L167: isolated marker/symbol line :: '</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr"/>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>L292: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen :: _----------</t>
+        </is>
+      </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
@@ -1030,16 +1022,8 @@
           <t>L460: suspicious token(s): 3i (letter/digit mix) :: _*.3i is aware of it.</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L902: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Mr. J. W. Nelles, son of Dr. Nelles, of</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L171: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Oâ€™Leary succeeded in placing their man at</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1051,7 +1035,7 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L313: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: - -------------------â€” -----â€” this city and had him arrested- than that ho was coupling cars and got</t>
+          <t>L313: punctuation artifact: double/multiple hyphen :: - -------------------— -----— this city and had him arrested- than that ho was coupling cars and got</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -1085,7 +1069,7 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>L710: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SoUTHAMPToN (odd internal casing) :: SoUTHAMPToN, July 5.â€” A most disastrous</t>
+          <t>L710: suspicious token(s): SoUTHAMPToN (odd internal casing) :: SoUTHAMPToN, July 5.— A most disastrous</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
@@ -1093,16 +1077,8 @@
           <t>L502: suspicious token(s): a5 (letter/digit mix) :: afternoon. The house and contents were a5</t>
         </is>
       </c>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L937: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Men's class.â€” 100 yard race-1st M. Simons,</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L185: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and asked for Mr. Riversâ€™ mail,</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1153,19 +1129,11 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): VanArsdale (odd internal casing) :: midnight. The fire started in VanArsdaleâ€™s</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L962: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Says an Ancaster correspondent:</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L215: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: from a man named Moir, of St. Maryâ€™s.</t>
-        </is>
-      </c>
+          <t>L568: suspicious token(s): VanArsdale’s (odd internal casing) :: midnight. The fire started in VanArsdale’s</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1197,12 +1165,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1220,11 +1188,7 @@
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ended in Brownâ€™s capture. Miss Benjamin</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1261,7 +1225,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1275,15 +1239,11 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L627: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 1thousand (letter/digit mix) :: â€”1thousand dollars will not cover Mr. Swan-</t>
+          <t>L627: suspicious token(s): 1thousand (letter/digit mix) :: —1thousand dollars will not cover Mr. Swan-</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L236: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the letter during the detectiveâ€™s absence,</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1295,7 +1255,7 @@
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L478: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | punctuation artifact: repeated periods :: the night of the fire he was awakened byâ€˜or...-</t>
+          <t>L478: punctuation artifact: repeated periods :: the night of the fire he was awakened by‘or...-</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1320,7 +1280,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1338,16 +1298,12 @@
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L264: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ideâ€™s odase drownclaimsthat by the detectives in the hope that they</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L483: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L483: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1389,15 +1345,11 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L653: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 118Y (letter/digit mix) :: offering Bad Meat for Sale. |jump.â€”1st M. Simons, distance 118Y</t>
+          <t>L653: suspicious token(s): 118Y (letter/digit mix) :: offering Bad Meat for Sale. |jump.—1st M. Simons, distance 118Y</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L266: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods | suspicious token(s): ticulari9 (letter/digit mix), SEESaeoeetet (odd internal casing) :: p^lygamistic proclivities. â€¢esn The - a*ticulari9 Mousse E...SEESaeoeetet</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1444,15 +1396,11 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>L661: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 24feet (letter/digit mix) :: growing sections of Delaware and Mary- of the vealâ€”Thomas Hines, Charles Hines | inches ; 2nd W. J. McGuire, 24feet.Distance 75</t>
+          <t>L661: suspicious token(s): 24feet (letter/digit mix) :: growing sections of Delaware and Mary- of the veal—Thomas Hines, Charles Hines | inches ; 2nd W. J. McGuire, 24feet.Distance 75</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L267: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: -------------------m ---------â€” ever, can be detected by the dateof the nearer than Gibbonsâ€™ which heing a black satchel and sitting on a road.</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1464,7 +1412,7 @@
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): under12 (letter/digit mix) :: __________________--Magistrate for disregarding the city by-law Boysâ€™ race, under12 yearsof age Distance 75</t>
+          <t>L665: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): under12 (letter/digit mix) :: __________________--Magistrate for disregarding the city by-law Boys’ race, under12 yearsof age Distance 75</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
@@ -1499,15 +1447,11 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): under12 (letter/digit mix) :: __________________--Magistrate for disregarding the city by-law Boysâ€™ race, under12 yearsof age Distance 75</t>
+          <t>L665: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): under12 (letter/digit mix) :: __________________--Magistrate for disregarding the city by-law Boys’ race, under12 yearsof age Distance 75</t>
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L286: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: officers. torious criminalsâ€”Johnston and Big Ed. of finding out the real factsof the case, and top cost which lay beside him on the seat</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
@@ -1519,7 +1463,7 @@
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: county), has been successful in carrying off were fined $5, or 30 days in jail, and the --â€”.</t>
+          <t>L672: punctuation artifact: double/multiple hyphen :: county), has been successful in carrying off were fined $5, or 30 days in jail, and the --—.</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
@@ -1558,11 +1502,7 @@
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L288: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Next Wednesday the annual excursion of Riceâ€”who have been preyinguponthe whether Lecce should be defended or not. I and asked the petticoated man to pick it</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1574,7 +1514,7 @@
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L677: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: has been summoned by telegraph to Mani |-+ â€” â€” ------â€¢ ------â€” a nosriogole owned by James</t>
+          <t>L677: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen; hyphen/bullet debris :: has been summoned by telegraph to Mani |-+ — — ------• ------— a nosriogole owned by James</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
@@ -1609,15 +1549,11 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): T0Lateral (letter/digit mix) :: dive for the baby, while Mrs. Nellesand â€”His many friends T0Lateral</t>
+          <t>L684: suspicious token(s): T0Lateral (letter/digit mix) :: dive for the baby, while Mrs. Nellesand —His many friends T0Lateral</t>
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L298: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): ThePeel (odd internal casing) :: â€œThe examination for teachers' certifi- At the Police Court this morning James velopmentetar conduct at thetime ofthe carried were found two revolvers. ThePeel</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1652,11 +1588,7 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: E - - â€” =â€” c</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1691,11 +1623,7 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L306: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN, U+00A4 CURRENCY SIGN | suspicious token(s): neWelaeCANT (odd internal casing) :: 0-3 - -aà¥¤^^^neWelaeCANT</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1715,1308 +1643,6 @@
       <c r="X19" s="1" t="inlineStr"/>
       <c r="Y19" s="1" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr"/>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr"/>
-      <c r="D20" s="1" t="inlineStr"/>
-      <c r="E20" s="1" t="inlineStr"/>
-      <c r="F20" s="1" t="inlineStr"/>
-      <c r="G20" s="1" t="inlineStr"/>
-      <c r="H20" s="1" t="inlineStr"/>
-      <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L313: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: - -------------------â€” -----â€” this city and had him arrested- than that ho was coupling cars and got</t>
-        </is>
-      </c>
-      <c r="L20" s="1" t="inlineStr"/>
-      <c r="M20" s="1" t="inlineStr"/>
-      <c r="N20" s="1" t="inlineStr"/>
-      <c r="O20" s="1" t="inlineStr"/>
-      <c r="P20" s="1" t="inlineStr"/>
-      <c r="Q20" s="1" t="inlineStr"/>
-      <c r="R20" s="1" t="inlineStr"/>
-      <c r="S20" s="1" t="inlineStr"/>
-      <c r="T20" s="1" t="inlineStr"/>
-      <c r="U20" s="1" t="inlineStr"/>
-      <c r="V20" s="1" t="inlineStr"/>
-      <c r="W20" s="1" t="inlineStr"/>
-      <c r="X20" s="1" t="inlineStr"/>
-      <c r="Y20" s="1" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr"/>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr"/>
-      <c r="D21" s="1" t="inlineStr"/>
-      <c r="E21" s="1" t="inlineStr"/>
-      <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="1" t="inlineStr"/>
-      <c r="H21" s="1" t="inlineStr"/>
-      <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L361: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: SYRACUSE, N.Y., July 5.â€”In the bicycle</t>
-        </is>
-      </c>
-      <c r="L21" s="1" t="inlineStr"/>
-      <c r="M21" s="1" t="inlineStr"/>
-      <c r="N21" s="1" t="inlineStr"/>
-      <c r="O21" s="1" t="inlineStr"/>
-      <c r="P21" s="1" t="inlineStr"/>
-      <c r="Q21" s="1" t="inlineStr"/>
-      <c r="R21" s="1" t="inlineStr"/>
-      <c r="S21" s="1" t="inlineStr"/>
-      <c r="T21" s="1" t="inlineStr"/>
-      <c r="U21" s="1" t="inlineStr"/>
-      <c r="V21" s="1" t="inlineStr"/>
-      <c r="W21" s="1" t="inlineStr"/>
-      <c r="X21" s="1" t="inlineStr"/>
-      <c r="Y21" s="1" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr"/>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr"/>
-      <c r="D22" s="1" t="inlineStr"/>
-      <c r="E22" s="1" t="inlineStr"/>
-      <c r="F22" s="1" t="inlineStr"/>
-      <c r="G22" s="1" t="inlineStr"/>
-      <c r="H22" s="1" t="inlineStr"/>
-      <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L370: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LONDON, July 6.â€”The race for the mid-</t>
-        </is>
-      </c>
-      <c r="L22" s="1" t="inlineStr"/>
-      <c r="M22" s="1" t="inlineStr"/>
-      <c r="N22" s="1" t="inlineStr"/>
-      <c r="O22" s="1" t="inlineStr"/>
-      <c r="P22" s="1" t="inlineStr"/>
-      <c r="Q22" s="1" t="inlineStr"/>
-      <c r="R22" s="1" t="inlineStr"/>
-      <c r="S22" s="1" t="inlineStr"/>
-      <c r="T22" s="1" t="inlineStr"/>
-      <c r="U22" s="1" t="inlineStr"/>
-      <c r="V22" s="1" t="inlineStr"/>
-      <c r="W22" s="1" t="inlineStr"/>
-      <c r="X22" s="1" t="inlineStr"/>
-      <c r="Y22" s="1" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr"/>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr"/>
-      <c r="D23" s="1" t="inlineStr"/>
-      <c r="E23" s="1" t="inlineStr"/>
-      <c r="F23" s="1" t="inlineStr"/>
-      <c r="G23" s="1" t="inlineStr"/>
-      <c r="H23" s="1" t="inlineStr"/>
-      <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L373: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Lord Lurganâ€™s Cotillion second, and Lord</t>
-        </is>
-      </c>
-      <c r="L23" s="1" t="inlineStr"/>
-      <c r="M23" s="1" t="inlineStr"/>
-      <c r="N23" s="1" t="inlineStr"/>
-      <c r="O23" s="1" t="inlineStr"/>
-      <c r="P23" s="1" t="inlineStr"/>
-      <c r="Q23" s="1" t="inlineStr"/>
-      <c r="R23" s="1" t="inlineStr"/>
-      <c r="S23" s="1" t="inlineStr"/>
-      <c r="T23" s="1" t="inlineStr"/>
-      <c r="U23" s="1" t="inlineStr"/>
-      <c r="V23" s="1" t="inlineStr"/>
-      <c r="W23" s="1" t="inlineStr"/>
-      <c r="X23" s="1" t="inlineStr"/>
-      <c r="Y23" s="1" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr"/>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr"/>
-      <c r="D24" s="1" t="inlineStr"/>
-      <c r="E24" s="1" t="inlineStr"/>
-      <c r="F24" s="1" t="inlineStr"/>
-      <c r="G24" s="1" t="inlineStr"/>
-      <c r="H24" s="1" t="inlineStr"/>
-      <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L374: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Calthorpeâ€™s Devote third.</t>
-        </is>
-      </c>
-      <c r="L24" s="1" t="inlineStr"/>
-      <c r="M24" s="1" t="inlineStr"/>
-      <c r="N24" s="1" t="inlineStr"/>
-      <c r="O24" s="1" t="inlineStr"/>
-      <c r="P24" s="1" t="inlineStr"/>
-      <c r="Q24" s="1" t="inlineStr"/>
-      <c r="R24" s="1" t="inlineStr"/>
-      <c r="S24" s="1" t="inlineStr"/>
-      <c r="T24" s="1" t="inlineStr"/>
-      <c r="U24" s="1" t="inlineStr"/>
-      <c r="V24" s="1" t="inlineStr"/>
-      <c r="W24" s="1" t="inlineStr"/>
-      <c r="X24" s="1" t="inlineStr"/>
-      <c r="Y24" s="1" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr"/>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr"/>
-      <c r="D25" s="1" t="inlineStr"/>
-      <c r="E25" s="1" t="inlineStr"/>
-      <c r="F25" s="1" t="inlineStr"/>
-      <c r="G25" s="1" t="inlineStr"/>
-      <c r="H25" s="1" t="inlineStr"/>
-      <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L382: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Sr. THOMAS, July 6.â€”Yesterday was the</t>
-        </is>
-      </c>
-      <c r="L25" s="1" t="inlineStr"/>
-      <c r="M25" s="1" t="inlineStr"/>
-      <c r="N25" s="1" t="inlineStr"/>
-      <c r="O25" s="1" t="inlineStr"/>
-      <c r="P25" s="1" t="inlineStr"/>
-      <c r="Q25" s="1" t="inlineStr"/>
-      <c r="R25" s="1" t="inlineStr"/>
-      <c r="S25" s="1" t="inlineStr"/>
-      <c r="T25" s="1" t="inlineStr"/>
-      <c r="U25" s="1" t="inlineStr"/>
-      <c r="V25" s="1" t="inlineStr"/>
-      <c r="W25" s="1" t="inlineStr"/>
-      <c r="X25" s="1" t="inlineStr"/>
-      <c r="Y25" s="1" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr"/>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr"/>
-      <c r="D26" s="1" t="inlineStr"/>
-      <c r="E26" s="1" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr"/>
-      <c r="G26" s="1" t="inlineStr"/>
-      <c r="H26" s="1" t="inlineStr"/>
-      <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L420: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: " Anâ€™ what would be the use of lavinâ€™ it</t>
-        </is>
-      </c>
-      <c r="L26" s="1" t="inlineStr"/>
-      <c r="M26" s="1" t="inlineStr"/>
-      <c r="N26" s="1" t="inlineStr"/>
-      <c r="O26" s="1" t="inlineStr"/>
-      <c r="P26" s="1" t="inlineStr"/>
-      <c r="Q26" s="1" t="inlineStr"/>
-      <c r="R26" s="1" t="inlineStr"/>
-      <c r="S26" s="1" t="inlineStr"/>
-      <c r="T26" s="1" t="inlineStr"/>
-      <c r="U26" s="1" t="inlineStr"/>
-      <c r="V26" s="1" t="inlineStr"/>
-      <c r="W26" s="1" t="inlineStr"/>
-      <c r="X26" s="1" t="inlineStr"/>
-      <c r="Y26" s="1" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr"/>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr"/>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr"/>
-      <c r="G27" s="1" t="inlineStr"/>
-      <c r="H27" s="1" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L466: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Cayuga, Haldimand county, was burned,â€”</t>
-        </is>
-      </c>
-      <c r="L27" s="1" t="inlineStr"/>
-      <c r="M27" s="1" t="inlineStr"/>
-      <c r="N27" s="1" t="inlineStr"/>
-      <c r="O27" s="1" t="inlineStr"/>
-      <c r="P27" s="1" t="inlineStr"/>
-      <c r="Q27" s="1" t="inlineStr"/>
-      <c r="R27" s="1" t="inlineStr"/>
-      <c r="S27" s="1" t="inlineStr"/>
-      <c r="T27" s="1" t="inlineStr"/>
-      <c r="U27" s="1" t="inlineStr"/>
-      <c r="V27" s="1" t="inlineStr"/>
-      <c r="W27" s="1" t="inlineStr"/>
-      <c r="X27" s="1" t="inlineStr"/>
-      <c r="Y27" s="1" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr"/>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr"/>
-      <c r="D28" s="1" t="inlineStr"/>
-      <c r="E28" s="1" t="inlineStr"/>
-      <c r="F28" s="1" t="inlineStr"/>
-      <c r="G28" s="1" t="inlineStr"/>
-      <c r="H28" s="1" t="inlineStr"/>
-      <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L478: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE | punctuation artifact: repeated periods :: the night of the fire he was awakened byâ€˜or...-</t>
-        </is>
-      </c>
-      <c r="L28" s="1" t="inlineStr"/>
-      <c r="M28" s="1" t="inlineStr"/>
-      <c r="N28" s="1" t="inlineStr"/>
-      <c r="O28" s="1" t="inlineStr"/>
-      <c r="P28" s="1" t="inlineStr"/>
-      <c r="Q28" s="1" t="inlineStr"/>
-      <c r="R28" s="1" t="inlineStr"/>
-      <c r="S28" s="1" t="inlineStr"/>
-      <c r="T28" s="1" t="inlineStr"/>
-      <c r="U28" s="1" t="inlineStr"/>
-      <c r="V28" s="1" t="inlineStr"/>
-      <c r="W28" s="1" t="inlineStr"/>
-      <c r="X28" s="1" t="inlineStr"/>
-      <c r="Y28" s="1" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr"/>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr"/>
-      <c r="D29" s="1" t="inlineStr"/>
-      <c r="E29" s="1" t="inlineStr"/>
-      <c r="F29" s="1" t="inlineStr"/>
-      <c r="G29" s="1" t="inlineStr"/>
-      <c r="H29" s="1" t="inlineStr"/>
-      <c r="I29" s="1" t="inlineStr"/>
-      <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L485: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Family ?â€”A Peculiar Case.</t>
-        </is>
-      </c>
-      <c r="L29" s="1" t="inlineStr"/>
-      <c r="M29" s="1" t="inlineStr"/>
-      <c r="N29" s="1" t="inlineStr"/>
-      <c r="O29" s="1" t="inlineStr"/>
-      <c r="P29" s="1" t="inlineStr"/>
-      <c r="Q29" s="1" t="inlineStr"/>
-      <c r="R29" s="1" t="inlineStr"/>
-      <c r="S29" s="1" t="inlineStr"/>
-      <c r="T29" s="1" t="inlineStr"/>
-      <c r="U29" s="1" t="inlineStr"/>
-      <c r="V29" s="1" t="inlineStr"/>
-      <c r="W29" s="1" t="inlineStr"/>
-      <c r="X29" s="1" t="inlineStr"/>
-      <c r="Y29" s="1" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr"/>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr"/>
-      <c r="D30" s="1" t="inlineStr"/>
-      <c r="E30" s="1" t="inlineStr"/>
-      <c r="F30" s="1" t="inlineStr"/>
-      <c r="G30" s="1" t="inlineStr"/>
-      <c r="H30" s="1" t="inlineStr"/>
-      <c r="I30" s="1" t="inlineStr"/>
-      <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L498: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NAPANEE, Ont., July 4.â€”A frame house,</t>
-        </is>
-      </c>
-      <c r="L30" s="1" t="inlineStr"/>
-      <c r="M30" s="1" t="inlineStr"/>
-      <c r="N30" s="1" t="inlineStr"/>
-      <c r="O30" s="1" t="inlineStr"/>
-      <c r="P30" s="1" t="inlineStr"/>
-      <c r="Q30" s="1" t="inlineStr"/>
-      <c r="R30" s="1" t="inlineStr"/>
-      <c r="S30" s="1" t="inlineStr"/>
-      <c r="T30" s="1" t="inlineStr"/>
-      <c r="U30" s="1" t="inlineStr"/>
-      <c r="V30" s="1" t="inlineStr"/>
-      <c r="W30" s="1" t="inlineStr"/>
-      <c r="X30" s="1" t="inlineStr"/>
-      <c r="Y30" s="1" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr"/>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr"/>
-      <c r="D31" s="1" t="inlineStr"/>
-      <c r="E31" s="1" t="inlineStr"/>
-      <c r="F31" s="1" t="inlineStr"/>
-      <c r="G31" s="1" t="inlineStr"/>
-      <c r="H31" s="1" t="inlineStr"/>
-      <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WINNIPEG, July 4.â€”A livery stable</t>
-        </is>
-      </c>
-      <c r="L31" s="1" t="inlineStr"/>
-      <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr"/>
-      <c r="O31" s="1" t="inlineStr"/>
-      <c r="P31" s="1" t="inlineStr"/>
-      <c r="Q31" s="1" t="inlineStr"/>
-      <c r="R31" s="1" t="inlineStr"/>
-      <c r="S31" s="1" t="inlineStr"/>
-      <c r="T31" s="1" t="inlineStr"/>
-      <c r="U31" s="1" t="inlineStr"/>
-      <c r="V31" s="1" t="inlineStr"/>
-      <c r="W31" s="1" t="inlineStr"/>
-      <c r="X31" s="1" t="inlineStr"/>
-      <c r="Y31" s="1" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr"/>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" s="1" t="inlineStr"/>
-      <c r="D32" s="1" t="inlineStr"/>
-      <c r="E32" s="1" t="inlineStr"/>
-      <c r="F32" s="1" t="inlineStr"/>
-      <c r="G32" s="1" t="inlineStr"/>
-      <c r="H32" s="1" t="inlineStr"/>
-      <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L510: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SOUTHAMPTON, July 5.â€”A most disastrous</t>
-        </is>
-      </c>
-      <c r="L32" s="1" t="inlineStr"/>
-      <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="inlineStr"/>
-      <c r="O32" s="1" t="inlineStr"/>
-      <c r="P32" s="1" t="inlineStr"/>
-      <c r="Q32" s="1" t="inlineStr"/>
-      <c r="R32" s="1" t="inlineStr"/>
-      <c r="S32" s="1" t="inlineStr"/>
-      <c r="T32" s="1" t="inlineStr"/>
-      <c r="U32" s="1" t="inlineStr"/>
-      <c r="V32" s="1" t="inlineStr"/>
-      <c r="W32" s="1" t="inlineStr"/>
-      <c r="X32" s="1" t="inlineStr"/>
-      <c r="Y32" s="1" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr"/>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr"/>
-      <c r="D33" s="1" t="inlineStr"/>
-      <c r="E33" s="1" t="inlineStr"/>
-      <c r="F33" s="1" t="inlineStr"/>
-      <c r="G33" s="1" t="inlineStr"/>
-      <c r="H33" s="1" t="inlineStr"/>
-      <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L529: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MARYSVILLE, Cal., July 5.â€”A disastrous</t>
-        </is>
-      </c>
-      <c r="L33" s="1" t="inlineStr"/>
-      <c r="M33" s="1" t="inlineStr"/>
-      <c r="N33" s="1" t="inlineStr"/>
-      <c r="O33" s="1" t="inlineStr"/>
-      <c r="P33" s="1" t="inlineStr"/>
-      <c r="Q33" s="1" t="inlineStr"/>
-      <c r="R33" s="1" t="inlineStr"/>
-      <c r="S33" s="1" t="inlineStr"/>
-      <c r="T33" s="1" t="inlineStr"/>
-      <c r="U33" s="1" t="inlineStr"/>
-      <c r="V33" s="1" t="inlineStr"/>
-      <c r="W33" s="1" t="inlineStr"/>
-      <c r="X33" s="1" t="inlineStr"/>
-      <c r="Y33" s="1" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr"/>
-      <c r="B34" s="1" t="inlineStr"/>
-      <c r="C34" s="1" t="inlineStr"/>
-      <c r="D34" s="1" t="inlineStr"/>
-      <c r="E34" s="1" t="inlineStr"/>
-      <c r="F34" s="1" t="inlineStr"/>
-      <c r="G34" s="1" t="inlineStr"/>
-      <c r="H34" s="1" t="inlineStr"/>
-      <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L532: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: an hourâ€™s adjournment.</t>
-        </is>
-      </c>
-      <c r="L34" s="1" t="inlineStr"/>
-      <c r="M34" s="1" t="inlineStr"/>
-      <c r="N34" s="1" t="inlineStr"/>
-      <c r="O34" s="1" t="inlineStr"/>
-      <c r="P34" s="1" t="inlineStr"/>
-      <c r="Q34" s="1" t="inlineStr"/>
-      <c r="R34" s="1" t="inlineStr"/>
-      <c r="S34" s="1" t="inlineStr"/>
-      <c r="T34" s="1" t="inlineStr"/>
-      <c r="U34" s="1" t="inlineStr"/>
-      <c r="V34" s="1" t="inlineStr"/>
-      <c r="W34" s="1" t="inlineStr"/>
-      <c r="X34" s="1" t="inlineStr"/>
-      <c r="Y34" s="1" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr"/>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr"/>
-      <c r="D35" s="1" t="inlineStr"/>
-      <c r="E35" s="1" t="inlineStr"/>
-      <c r="F35" s="1" t="inlineStr"/>
-      <c r="G35" s="1" t="inlineStr"/>
-      <c r="H35" s="1" t="inlineStr"/>
-      <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: panionâ€”and his coatâ€”far behind. A STANTON, Mich., July 5.â€”The entire south</t>
-        </is>
-      </c>
-      <c r="L35" s="1" t="inlineStr"/>
-      <c r="M35" s="1" t="inlineStr"/>
-      <c r="N35" s="1" t="inlineStr"/>
-      <c r="O35" s="1" t="inlineStr"/>
-      <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr"/>
-      <c r="R35" s="1" t="inlineStr"/>
-      <c r="S35" s="1" t="inlineStr"/>
-      <c r="T35" s="1" t="inlineStr"/>
-      <c r="U35" s="1" t="inlineStr"/>
-      <c r="V35" s="1" t="inlineStr"/>
-      <c r="W35" s="1" t="inlineStr"/>
-      <c r="X35" s="1" t="inlineStr"/>
-      <c r="Y35" s="1" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr"/>
-      <c r="B36" s="1" t="inlineStr"/>
-      <c r="C36" s="1" t="inlineStr"/>
-      <c r="D36" s="1" t="inlineStr"/>
-      <c r="E36" s="1" t="inlineStr"/>
-      <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="1" t="inlineStr"/>
-      <c r="H36" s="1" t="inlineStr"/>
-      <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L566: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CADILLAC, Mich., July 5.â€”The business</t>
-        </is>
-      </c>
-      <c r="L36" s="1" t="inlineStr"/>
-      <c r="M36" s="1" t="inlineStr"/>
-      <c r="N36" s="1" t="inlineStr"/>
-      <c r="O36" s="1" t="inlineStr"/>
-      <c r="P36" s="1" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr"/>
-      <c r="R36" s="1" t="inlineStr"/>
-      <c r="S36" s="1" t="inlineStr"/>
-      <c r="T36" s="1" t="inlineStr"/>
-      <c r="U36" s="1" t="inlineStr"/>
-      <c r="V36" s="1" t="inlineStr"/>
-      <c r="W36" s="1" t="inlineStr"/>
-      <c r="X36" s="1" t="inlineStr"/>
-      <c r="Y36" s="1" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr"/>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" s="1" t="inlineStr"/>
-      <c r="D37" s="1" t="inlineStr"/>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr"/>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): VanArsdale (odd internal casing) :: midnight. The fire started in VanArsdaleâ€™s</t>
-        </is>
-      </c>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr"/>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr"/>
-      <c r="R37" s="1" t="inlineStr"/>
-      <c r="S37" s="1" t="inlineStr"/>
-      <c r="T37" s="1" t="inlineStr"/>
-      <c r="U37" s="1" t="inlineStr"/>
-      <c r="V37" s="1" t="inlineStr"/>
-      <c r="W37" s="1" t="inlineStr"/>
-      <c r="X37" s="1" t="inlineStr"/>
-      <c r="Y37" s="1" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr"/>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" s="1" t="inlineStr"/>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr"/>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L606: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: no insurance. â€˜I here was no fire protection,</t>
-        </is>
-      </c>
-      <c r="L38" s="1" t="inlineStr"/>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr"/>
-      <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr"/>
-      <c r="R38" s="1" t="inlineStr"/>
-      <c r="S38" s="1" t="inlineStr"/>
-      <c r="T38" s="1" t="inlineStr"/>
-      <c r="U38" s="1" t="inlineStr"/>
-      <c r="V38" s="1" t="inlineStr"/>
-      <c r="W38" s="1" t="inlineStr"/>
-      <c r="X38" s="1" t="inlineStr"/>
-      <c r="Y38" s="1" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr"/>
-      <c r="B39" s="1" t="inlineStr"/>
-      <c r="C39" s="1" t="inlineStr"/>
-      <c r="D39" s="1" t="inlineStr"/>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L608: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: rest which is the inalienable right of the 4 oâ€™clock this morning.</t>
-        </is>
-      </c>
-      <c r="L39" s="1" t="inlineStr"/>
-      <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr"/>
-      <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr"/>
-      <c r="R39" s="1" t="inlineStr"/>
-      <c r="S39" s="1" t="inlineStr"/>
-      <c r="T39" s="1" t="inlineStr"/>
-      <c r="U39" s="1" t="inlineStr"/>
-      <c r="V39" s="1" t="inlineStr"/>
-      <c r="W39" s="1" t="inlineStr"/>
-      <c r="X39" s="1" t="inlineStr"/>
-      <c r="Y39" s="1" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr"/>
-      <c r="B40" s="1" t="inlineStr"/>
-      <c r="C40" s="1" t="inlineStr"/>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L617: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: it resol protest against this legalized Sab- LINDSAY, July 6.â€”Yesterday afternoon a</t>
-        </is>
-      </c>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr"/>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr"/>
-      <c r="R40" s="1" t="inlineStr"/>
-      <c r="S40" s="1" t="inlineStr"/>
-      <c r="T40" s="1" t="inlineStr"/>
-      <c r="U40" s="1" t="inlineStr"/>
-      <c r="V40" s="1" t="inlineStr"/>
-      <c r="W40" s="1" t="inlineStr"/>
-      <c r="X40" s="1" t="inlineStr"/>
-      <c r="Y40" s="1" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr"/>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" s="1" t="inlineStr"/>
-      <c r="D41" s="1" t="inlineStr"/>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr"/>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L627: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 1thousand (letter/digit mix) :: â€”1thousand dollars will not cover Mr. Swan-</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr"/>
-      <c r="R41" s="1" t="inlineStr"/>
-      <c r="S41" s="1" t="inlineStr"/>
-      <c r="T41" s="1" t="inlineStr"/>
-      <c r="U41" s="1" t="inlineStr"/>
-      <c r="V41" s="1" t="inlineStr"/>
-      <c r="W41" s="1" t="inlineStr"/>
-      <c r="X41" s="1" t="inlineStr"/>
-      <c r="Y41" s="1" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr"/>
-      <c r="B42" s="1" t="inlineStr"/>
-      <c r="C42" s="1" t="inlineStr"/>
-      <c r="D42" s="1" t="inlineStr"/>
-      <c r="E42" s="1" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr"/>
-      <c r="G42" s="1" t="inlineStr"/>
-      <c r="H42" s="1" t="inlineStr"/>
-      <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L631: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: A Warning to the Meddlesome. | CAMPBELLFORD, July 6.â€”The barn and</t>
-        </is>
-      </c>
-      <c r="L42" s="1" t="inlineStr"/>
-      <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr"/>
-      <c r="P42" s="1" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr"/>
-      <c r="R42" s="1" t="inlineStr"/>
-      <c r="S42" s="1" t="inlineStr"/>
-      <c r="T42" s="1" t="inlineStr"/>
-      <c r="U42" s="1" t="inlineStr"/>
-      <c r="V42" s="1" t="inlineStr"/>
-      <c r="W42" s="1" t="inlineStr"/>
-      <c r="X42" s="1" t="inlineStr"/>
-      <c r="Y42" s="1" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr"/>
-      <c r="B43" s="1" t="inlineStr"/>
-      <c r="C43" s="1" t="inlineStr"/>
-      <c r="D43" s="1" t="inlineStr"/>
-      <c r="E43" s="1" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr"/>
-      <c r="G43" s="1" t="inlineStr"/>
-      <c r="H43" s="1" t="inlineStr"/>
-      <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L639: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | missing space around punctuation :: on the seat,and a lady sitting opposite be- ________________, â€”</t>
-        </is>
-      </c>
-      <c r="L43" s="1" t="inlineStr"/>
-      <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr"/>
-      <c r="P43" s="1" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr"/>
-      <c r="R43" s="1" t="inlineStr"/>
-      <c r="S43" s="1" t="inlineStr"/>
-      <c r="T43" s="1" t="inlineStr"/>
-      <c r="U43" s="1" t="inlineStr"/>
-      <c r="V43" s="1" t="inlineStr"/>
-      <c r="W43" s="1" t="inlineStr"/>
-      <c r="X43" s="1" t="inlineStr"/>
-      <c r="Y43" s="1" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr"/>
-      <c r="B44" s="1" t="inlineStr"/>
-      <c r="C44" s="1" t="inlineStr"/>
-      <c r="D44" s="1" t="inlineStr"/>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr"/>
-      <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr"/>
-      <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L647: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Sergeant-Major about the boy, who has the Men's class.â€”100 yard raceâ€”1st M. Simons,</t>
-        </is>
-      </c>
-      <c r="L44" s="1" t="inlineStr"/>
-      <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr"/>
-      <c r="P44" s="1" t="inlineStr"/>
-      <c r="Q44" s="1" t="inlineStr"/>
-      <c r="R44" s="1" t="inlineStr"/>
-      <c r="S44" s="1" t="inlineStr"/>
-      <c r="T44" s="1" t="inlineStr"/>
-      <c r="U44" s="1" t="inlineStr"/>
-      <c r="V44" s="1" t="inlineStr"/>
-      <c r="W44" s="1" t="inlineStr"/>
-      <c r="X44" s="1" t="inlineStr"/>
-      <c r="Y44" s="1" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr"/>
-      <c r="B45" s="1" t="inlineStr"/>
-      <c r="C45" s="1" t="inlineStr"/>
-      <c r="D45" s="1" t="inlineStr"/>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L650: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: was decided to remand him for 8. Three-legged race.â€”1st J. and A., Henderson, ment and to the press.</t>
-        </is>
-      </c>
-      <c r="L45" s="1" t="inlineStr"/>
-      <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr"/>
-      <c r="P45" s="1" t="inlineStr"/>
-      <c r="Q45" s="1" t="inlineStr"/>
-      <c r="R45" s="1" t="inlineStr"/>
-      <c r="S45" s="1" t="inlineStr"/>
-      <c r="T45" s="1" t="inlineStr"/>
-      <c r="U45" s="1" t="inlineStr"/>
-      <c r="V45" s="1" t="inlineStr"/>
-      <c r="W45" s="1" t="inlineStr"/>
-      <c r="X45" s="1" t="inlineStr"/>
-      <c r="Y45" s="1" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr"/>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" s="1" t="inlineStr"/>
-      <c r="D46" s="1" t="inlineStr"/>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr"/>
-      <c r="G46" s="1" t="inlineStr"/>
-      <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L653: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 118Y (letter/digit mix) :: offering Bad Meat for Sale. |jump.â€”1st M. Simons, distance 118Y</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="inlineStr"/>
-      <c r="M46" s="1" t="inlineStr"/>
-      <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr"/>
-      <c r="P46" s="1" t="inlineStr"/>
-      <c r="Q46" s="1" t="inlineStr"/>
-      <c r="R46" s="1" t="inlineStr"/>
-      <c r="S46" s="1" t="inlineStr"/>
-      <c r="T46" s="1" t="inlineStr"/>
-      <c r="U46" s="1" t="inlineStr"/>
-      <c r="V46" s="1" t="inlineStr"/>
-      <c r="W46" s="1" t="inlineStr"/>
-      <c r="X46" s="1" t="inlineStr"/>
-      <c r="Y46" s="1" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr"/>
-      <c r="B47" s="1" t="inlineStr"/>
-      <c r="C47" s="1" t="inlineStr"/>
-      <c r="D47" s="1" t="inlineStr"/>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr"/>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L657: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: through the markets and came across no | Running hop, step and jump.â€”1st W. Van-</t>
-        </is>
-      </c>
-      <c r="L47" s="1" t="inlineStr"/>
-      <c r="M47" s="1" t="inlineStr"/>
-      <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
-      <c r="P47" s="1" t="inlineStr"/>
-      <c r="Q47" s="1" t="inlineStr"/>
-      <c r="R47" s="1" t="inlineStr"/>
-      <c r="S47" s="1" t="inlineStr"/>
-      <c r="T47" s="1" t="inlineStr"/>
-      <c r="U47" s="1" t="inlineStr"/>
-      <c r="V47" s="1" t="inlineStr"/>
-      <c r="W47" s="1" t="inlineStr"/>
-      <c r="X47" s="1" t="inlineStr"/>
-      <c r="Y47" s="1" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr"/>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" s="1" t="inlineStr"/>
-      <c r="D48" s="1" t="inlineStr"/>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr"/>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L660: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Reports from every county in the peach- I considered to be unfit for food. The owners I Putting the stone.â€”1st M. Simons, 24 feet 5</t>
-        </is>
-      </c>
-      <c r="L48" s="1" t="inlineStr"/>
-      <c r="M48" s="1" t="inlineStr"/>
-      <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr"/>
-      <c r="P48" s="1" t="inlineStr"/>
-      <c r="Q48" s="1" t="inlineStr"/>
-      <c r="R48" s="1" t="inlineStr"/>
-      <c r="S48" s="1" t="inlineStr"/>
-      <c r="T48" s="1" t="inlineStr"/>
-      <c r="U48" s="1" t="inlineStr"/>
-      <c r="V48" s="1" t="inlineStr"/>
-      <c r="W48" s="1" t="inlineStr"/>
-      <c r="X48" s="1" t="inlineStr"/>
-      <c r="Y48" s="1" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr"/>
-      <c r="B49" s="1" t="inlineStr"/>
-      <c r="C49" s="1" t="inlineStr"/>
-      <c r="D49" s="1" t="inlineStr"/>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr"/>
-      <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr"/>
-      <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L661: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 24feet (letter/digit mix) :: growing sections of Delaware and Mary- of the vealâ€”Thomas Hines, Charles Hines | inches ; 2nd W. J. McGuire, 24feet.Distance 75</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="inlineStr"/>
-      <c r="M49" s="1" t="inlineStr"/>
-      <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr"/>
-      <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="inlineStr"/>
-      <c r="R49" s="1" t="inlineStr"/>
-      <c r="S49" s="1" t="inlineStr"/>
-      <c r="T49" s="1" t="inlineStr"/>
-      <c r="U49" s="1" t="inlineStr"/>
-      <c r="V49" s="1" t="inlineStr"/>
-      <c r="W49" s="1" t="inlineStr"/>
-      <c r="X49" s="1" t="inlineStr"/>
-      <c r="Y49" s="1" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr"/>
-      <c r="B50" s="1" t="inlineStr"/>
-      <c r="C50" s="1" t="inlineStr"/>
-      <c r="D50" s="1" t="inlineStr"/>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr"/>
-      <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text | suspicious token(s): under12 (letter/digit mix) :: __________________--Magistrate for disregarding the city by-law Boysâ€™ race, under12 yearsof age Distance 75</t>
-        </is>
-      </c>
-      <c r="L50" s="1" t="inlineStr"/>
-      <c r="M50" s="1" t="inlineStr"/>
-      <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr"/>
-      <c r="P50" s="1" t="inlineStr"/>
-      <c r="Q50" s="1" t="inlineStr"/>
-      <c r="R50" s="1" t="inlineStr"/>
-      <c r="S50" s="1" t="inlineStr"/>
-      <c r="T50" s="1" t="inlineStr"/>
-      <c r="U50" s="1" t="inlineStr"/>
-      <c r="V50" s="1" t="inlineStr"/>
-      <c r="W50" s="1" t="inlineStr"/>
-      <c r="X50" s="1" t="inlineStr"/>
-      <c r="Y50" s="1" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr"/>
-      <c r="B51" s="1" t="inlineStr"/>
-      <c r="C51" s="1" t="inlineStr"/>
-      <c r="D51" s="1" t="inlineStr"/>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr"/>
-      <c r="G51" s="1" t="inlineStr"/>
-      <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L666: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . _______________â€ž . in offering the stuff for sale. The inspec- yardsâ€”1st George Wray, 2nd Patrick King, 3rd</t>
-        </is>
-      </c>
-      <c r="L51" s="1" t="inlineStr"/>
-      <c r="M51" s="1" t="inlineStr"/>
-      <c r="N51" s="1" t="inlineStr"/>
-      <c r="O51" s="1" t="inlineStr"/>
-      <c r="P51" s="1" t="inlineStr"/>
-      <c r="Q51" s="1" t="inlineStr"/>
-      <c r="R51" s="1" t="inlineStr"/>
-      <c r="S51" s="1" t="inlineStr"/>
-      <c r="T51" s="1" t="inlineStr"/>
-      <c r="U51" s="1" t="inlineStr"/>
-      <c r="V51" s="1" t="inlineStr"/>
-      <c r="W51" s="1" t="inlineStr"/>
-      <c r="X51" s="1" t="inlineStr"/>
-      <c r="Y51" s="1" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr"/>
-      <c r="B52" s="1" t="inlineStr"/>
-      <c r="C52" s="1" t="inlineStr"/>
-      <c r="D52" s="1" t="inlineStr"/>
-      <c r="E52" s="1" t="inlineStr"/>
-      <c r="F52" s="1" t="inlineStr"/>
-      <c r="G52" s="1" t="inlineStr"/>
-      <c r="H52" s="1" t="inlineStr"/>
-      <c r="I52" s="1" t="inlineStr"/>
-      <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L668: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: moved to Winona._judgment on meat was good, and that the yards.â€”1st Geo.Cairns, 2nd W. Lowry, 3rd Don-</t>
-        </is>
-      </c>
-      <c r="L52" s="1" t="inlineStr"/>
-      <c r="M52" s="1" t="inlineStr"/>
-      <c r="N52" s="1" t="inlineStr"/>
-      <c r="O52" s="1" t="inlineStr"/>
-      <c r="P52" s="1" t="inlineStr"/>
-      <c r="Q52" s="1" t="inlineStr"/>
-      <c r="R52" s="1" t="inlineStr"/>
-      <c r="S52" s="1" t="inlineStr"/>
-      <c r="T52" s="1" t="inlineStr"/>
-      <c r="U52" s="1" t="inlineStr"/>
-      <c r="V52" s="1" t="inlineStr"/>
-      <c r="W52" s="1" t="inlineStr"/>
-      <c r="X52" s="1" t="inlineStr"/>
-      <c r="Y52" s="1" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr"/>
-      <c r="B53" s="1" t="inlineStr"/>
-      <c r="C53" s="1" t="inlineStr"/>
-      <c r="D53" s="1" t="inlineStr"/>
-      <c r="E53" s="1" t="inlineStr"/>
-      <c r="F53" s="1" t="inlineStr"/>
-      <c r="G53" s="1" t="inlineStr"/>
-      <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr"/>
-      <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L670: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Mr. G. Harcourt, of St. Anns (Lincoln meat was bad. Each of the defendants | aid Stewart.</t>
-        </is>
-      </c>
-      <c r="L53" s="1" t="inlineStr"/>
-      <c r="M53" s="1" t="inlineStr"/>
-      <c r="N53" s="1" t="inlineStr"/>
-      <c r="O53" s="1" t="inlineStr"/>
-      <c r="P53" s="1" t="inlineStr"/>
-      <c r="Q53" s="1" t="inlineStr"/>
-      <c r="R53" s="1" t="inlineStr"/>
-      <c r="S53" s="1" t="inlineStr"/>
-      <c r="T53" s="1" t="inlineStr"/>
-      <c r="U53" s="1" t="inlineStr"/>
-      <c r="V53" s="1" t="inlineStr"/>
-      <c r="W53" s="1" t="inlineStr"/>
-      <c r="X53" s="1" t="inlineStr"/>
-      <c r="Y53" s="1" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr"/>
-      <c r="B54" s="1" t="inlineStr"/>
-      <c r="C54" s="1" t="inlineStr"/>
-      <c r="D54" s="1" t="inlineStr"/>
-      <c r="E54" s="1" t="inlineStr"/>
-      <c r="F54" s="1" t="inlineStr"/>
-      <c r="G54" s="1" t="inlineStr"/>
-      <c r="H54" s="1" t="inlineStr"/>
-      <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: county), has been successful in carrying off were fined $5, or 30 days in jail, and the --â€”.</t>
-        </is>
-      </c>
-      <c r="L54" s="1" t="inlineStr"/>
-      <c r="M54" s="1" t="inlineStr"/>
-      <c r="N54" s="1" t="inlineStr"/>
-      <c r="O54" s="1" t="inlineStr"/>
-      <c r="P54" s="1" t="inlineStr"/>
-      <c r="Q54" s="1" t="inlineStr"/>
-      <c r="R54" s="1" t="inlineStr"/>
-      <c r="S54" s="1" t="inlineStr"/>
-      <c r="T54" s="1" t="inlineStr"/>
-      <c r="U54" s="1" t="inlineStr"/>
-      <c r="V54" s="1" t="inlineStr"/>
-      <c r="W54" s="1" t="inlineStr"/>
-      <c r="X54" s="1" t="inlineStr"/>
-      <c r="Y54" s="1" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr"/>
-      <c r="B55" s="1" t="inlineStr"/>
-      <c r="C55" s="1" t="inlineStr"/>
-      <c r="D55" s="1" t="inlineStr"/>
-      <c r="E55" s="1" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="1" t="inlineStr"/>
-      <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L677: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: has been summoned by telegraph to Mani |-+ â€” â€” ------â€¢ ------â€” a nosriogole owned by James</t>
-        </is>
-      </c>
-      <c r="L55" s="1" t="inlineStr"/>
-      <c r="M55" s="1" t="inlineStr"/>
-      <c r="N55" s="1" t="inlineStr"/>
-      <c r="O55" s="1" t="inlineStr"/>
-      <c r="P55" s="1" t="inlineStr"/>
-      <c r="Q55" s="1" t="inlineStr"/>
-      <c r="R55" s="1" t="inlineStr"/>
-      <c r="S55" s="1" t="inlineStr"/>
-      <c r="T55" s="1" t="inlineStr"/>
-      <c r="U55" s="1" t="inlineStr"/>
-      <c r="V55" s="1" t="inlineStr"/>
-      <c r="W55" s="1" t="inlineStr"/>
-      <c r="X55" s="1" t="inlineStr"/>
-      <c r="Y55" s="1" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr"/>
-      <c r="B56" s="1" t="inlineStr"/>
-      <c r="C56" s="1" t="inlineStr"/>
-      <c r="D56" s="1" t="inlineStr"/>
-      <c r="E56" s="1" t="inlineStr"/>
-      <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="1" t="inlineStr"/>
-      <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L684: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): T0Lateral (letter/digit mix) :: dive for the baby, while Mrs. Nellesand â€”His many friends T0Lateral</t>
-        </is>
-      </c>
-      <c r="L56" s="1" t="inlineStr"/>
-      <c r="M56" s="1" t="inlineStr"/>
-      <c r="N56" s="1" t="inlineStr"/>
-      <c r="O56" s="1" t="inlineStr"/>
-      <c r="P56" s="1" t="inlineStr"/>
-      <c r="Q56" s="1" t="inlineStr"/>
-      <c r="R56" s="1" t="inlineStr"/>
-      <c r="S56" s="1" t="inlineStr"/>
-      <c r="T56" s="1" t="inlineStr"/>
-      <c r="U56" s="1" t="inlineStr"/>
-      <c r="V56" s="1" t="inlineStr"/>
-      <c r="W56" s="1" t="inlineStr"/>
-      <c r="X56" s="1" t="inlineStr"/>
-      <c r="Y56" s="1" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr"/>
-      <c r="B57" s="1" t="inlineStr"/>
-      <c r="C57" s="1" t="inlineStr"/>
-      <c r="D57" s="1" t="inlineStr"/>
-      <c r="E57" s="1" t="inlineStr"/>
-      <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr"/>
-      <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L698: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: him of his moneyâ€”about $4 or $5 in silver,</t>
-        </is>
-      </c>
-      <c r="L57" s="1" t="inlineStr"/>
-      <c r="M57" s="1" t="inlineStr"/>
-      <c r="N57" s="1" t="inlineStr"/>
-      <c r="O57" s="1" t="inlineStr"/>
-      <c r="P57" s="1" t="inlineStr"/>
-      <c r="Q57" s="1" t="inlineStr"/>
-      <c r="R57" s="1" t="inlineStr"/>
-      <c r="S57" s="1" t="inlineStr"/>
-      <c r="T57" s="1" t="inlineStr"/>
-      <c r="U57" s="1" t="inlineStr"/>
-      <c r="V57" s="1" t="inlineStr"/>
-      <c r="W57" s="1" t="inlineStr"/>
-      <c r="X57" s="1" t="inlineStr"/>
-      <c r="Y57" s="1" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr"/>
-      <c r="B58" s="1" t="inlineStr"/>
-      <c r="C58" s="1" t="inlineStr"/>
-      <c r="D58" s="1" t="inlineStr"/>
-      <c r="E58" s="1" t="inlineStr"/>
-      <c r="F58" s="1" t="inlineStr"/>
-      <c r="G58" s="1" t="inlineStr"/>
-      <c r="H58" s="1" t="inlineStr"/>
-      <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L725: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: too great she must replace the articles.â€”</t>
-        </is>
-      </c>
-      <c r="L58" s="1" t="inlineStr"/>
-      <c r="M58" s="1" t="inlineStr"/>
-      <c r="N58" s="1" t="inlineStr"/>
-      <c r="O58" s="1" t="inlineStr"/>
-      <c r="P58" s="1" t="inlineStr"/>
-      <c r="Q58" s="1" t="inlineStr"/>
-      <c r="R58" s="1" t="inlineStr"/>
-      <c r="S58" s="1" t="inlineStr"/>
-      <c r="T58" s="1" t="inlineStr"/>
-      <c r="U58" s="1" t="inlineStr"/>
-      <c r="V58" s="1" t="inlineStr"/>
-      <c r="W58" s="1" t="inlineStr"/>
-      <c r="X58" s="1" t="inlineStr"/>
-      <c r="Y58" s="1" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr"/>
-      <c r="B59" s="1" t="inlineStr"/>
-      <c r="C59" s="1" t="inlineStr"/>
-      <c r="D59" s="1" t="inlineStr"/>
-      <c r="E59" s="1" t="inlineStr"/>
-      <c r="F59" s="1" t="inlineStr"/>
-      <c r="G59" s="1" t="inlineStr"/>
-      <c r="H59" s="1" t="inlineStr"/>
-      <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”While Mr. A Marshall, of Middleport,</t>
-        </is>
-      </c>
-      <c r="L59" s="1" t="inlineStr"/>
-      <c r="M59" s="1" t="inlineStr"/>
-      <c r="N59" s="1" t="inlineStr"/>
-      <c r="O59" s="1" t="inlineStr"/>
-      <c r="P59" s="1" t="inlineStr"/>
-      <c r="Q59" s="1" t="inlineStr"/>
-      <c r="R59" s="1" t="inlineStr"/>
-      <c r="S59" s="1" t="inlineStr"/>
-      <c r="T59" s="1" t="inlineStr"/>
-      <c r="U59" s="1" t="inlineStr"/>
-      <c r="V59" s="1" t="inlineStr"/>
-      <c r="W59" s="1" t="inlineStr"/>
-      <c r="X59" s="1" t="inlineStr"/>
-      <c r="Y59" s="1" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr"/>
-      <c r="B60" s="1" t="inlineStr"/>
-      <c r="C60" s="1" t="inlineStr"/>
-      <c r="D60" s="1" t="inlineStr"/>
-      <c r="E60" s="1" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr"/>
-      <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L755: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: come out well honey will be soarce.â€”St.</t>
-        </is>
-      </c>
-      <c r="L60" s="1" t="inlineStr"/>
-      <c r="M60" s="1" t="inlineStr"/>
-      <c r="N60" s="1" t="inlineStr"/>
-      <c r="O60" s="1" t="inlineStr"/>
-      <c r="P60" s="1" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr"/>
-      <c r="R60" s="1" t="inlineStr"/>
-      <c r="S60" s="1" t="inlineStr"/>
-      <c r="T60" s="1" t="inlineStr"/>
-      <c r="U60" s="1" t="inlineStr"/>
-      <c r="V60" s="1" t="inlineStr"/>
-      <c r="W60" s="1" t="inlineStr"/>
-      <c r="X60" s="1" t="inlineStr"/>
-      <c r="Y60" s="1" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr"/>
-      <c r="B61" s="1" t="inlineStr"/>
-      <c r="C61" s="1" t="inlineStr"/>
-      <c r="D61" s="1" t="inlineStr"/>
-      <c r="E61" s="1" t="inlineStr"/>
-      <c r="F61" s="1" t="inlineStr"/>
-      <c r="G61" s="1" t="inlineStr"/>
-      <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr"/>
-      <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L756: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Catharines Journal.â€¢</t>
-        </is>
-      </c>
-      <c r="L61" s="1" t="inlineStr"/>
-      <c r="M61" s="1" t="inlineStr"/>
-      <c r="N61" s="1" t="inlineStr"/>
-      <c r="O61" s="1" t="inlineStr"/>
-      <c r="P61" s="1" t="inlineStr"/>
-      <c r="Q61" s="1" t="inlineStr"/>
-      <c r="R61" s="1" t="inlineStr"/>
-      <c r="S61" s="1" t="inlineStr"/>
-      <c r="T61" s="1" t="inlineStr"/>
-      <c r="U61" s="1" t="inlineStr"/>
-      <c r="V61" s="1" t="inlineStr"/>
-      <c r="W61" s="1" t="inlineStr"/>
-      <c r="X61" s="1" t="inlineStr"/>
-      <c r="Y61" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
